--- a/10. Equity/work/fundamentals_model/20260715_ファンダメンタルズの検討②/data/templates/05_factor_master_template.xlsx
+++ b/10. Equity/work/fundamentals_model/20260715_ファンダメンタルズの検討②/data/templates/05_factor_master_template.xlsx
@@ -2,11 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R567352f7d13a4367"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Factor_Master" sheetId="2" r:id="R668aa65fea9a4082"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Group_Settings" sheetId="3" r:id="R2c2020ba492a4619"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Group_Method_Params" sheetId="4" r:id="Rf6982ac1fd584380"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="5" r:id="Rd1da5fd349fa4f9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" r:id="R5987de5a227c4294"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Factor_Master" sheetId="2" r:id="Rf0d13125379d4990"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Group_Settings" sheetId="3" r:id="R18f09096a70e4c51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Group_Method_Params" sheetId="4" r:id="R78c44ea2548b41d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="5" r:id="R22aa2fef85df4458"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature_Engineering_Control" sheetId="6" r:id="R7621975ba6a2423b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Derived_Feature_Rules" sheetId="7" r:id="Rd3129ffcf05e4e85"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -44,7 +46,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -61,6 +63,16 @@
         <x:fgColor rgb="FF1F4E78"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -69,7 +81,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="30">
+  <x:cellXfs count="38">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -128,6 +140,24 @@
     <x:xf numFmtId="200" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -138,21 +168,21 @@
         <x:color rgb="FF7F7F7F"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9D9D9"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDEBF7"/>
         </x:patternFill>
       </x:fill>
@@ -310,10 +340,10 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="70" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="48" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="30" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="80" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -489,22 +519,40 @@
       <x:c r="D19" s="21"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="21"/>
-      <x:c r="B20" s="21"/>
-      <x:c r="C20" s="21"/>
-      <x:c r="D20" s="21"/>
+      <x:c r="A20" s="37" t="str">
+        <x:v>派生ファクター設定</x:v>
+      </x:c>
+      <x:c r="B20" s="37"/>
+      <x:c r="C20" s="37"/>
+      <x:c r="D20" s="37"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="21"/>
-      <x:c r="B21" s="21"/>
-      <x:c r="C21" s="21"/>
-      <x:c r="D21" s="21"/>
+      <x:c r="A21" s="21" t="str">
+        <x:v>Feature_Engineering_Control</x:v>
+      </x:c>
+      <x:c r="B21" s="21" t="str">
+        <x:v>グループまたは個別FAコード単位で派生特徴量の生成可否、all/selected、原系列利用を設定</x:v>
+      </x:c>
+      <x:c r="C21" s="21" t="str">
+        <x:v>分析担当者</x:v>
+      </x:c>
+      <x:c r="D21" s="21" t="str">
+        <x:v>factor指定がgroup指定より優先</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="21"/>
-      <x:c r="B22" s="21"/>
-      <x:c r="C22" s="21"/>
-      <x:c r="D22" s="21"/>
+      <x:c r="A22" s="21" t="str">
+        <x:v>Derived_Feature_Rules</x:v>
+      </x:c>
+      <x:c r="B22" s="21" t="str">
+        <x:v>差分・移動平均乖離等の生成式、窓、情報ラグ、利用可否を設定</x:v>
+      </x:c>
+      <x:c r="C22" s="21" t="str">
+        <x:v>モデル担当者</x:v>
+      </x:c>
+      <x:c r="D22" s="21" t="str">
+        <x:v>Source_Lag=1なら最新情報t-1と翌期リターンt+1の間隔は2時点</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="21"/>
@@ -513,14 +561,22 @@
       <x:c r="D23" s="21"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="21"/>
-      <x:c r="B24" s="21"/>
+      <x:c r="A24" s="21" t="str">
+        <x:v>時点整合</x:v>
+      </x:c>
+      <x:c r="B24" s="21" t="str">
+        <x:v>スコア時点tの派生値はt-Source_Lag以前の情報だけで作成し、forward_return=t+1と結合</x:v>
+      </x:c>
       <x:c r="C24" s="21"/>
       <x:c r="D24" s="21"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="21"/>
-      <x:c r="B25" s="21"/>
+      <x:c r="A25" s="21" t="str">
+        <x:v>Generation_Mode</x:v>
+      </x:c>
+      <x:c r="B25" s="21" t="str">
+        <x:v>all=Enabledなルールを全利用 / selected=EnabledかつSelected=1のみ利用</x:v>
+      </x:c>
       <x:c r="C25" s="21"/>
       <x:c r="D25" s="21"/>
     </x:row>
@@ -14331,4 +14387,447 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="48" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A1" s="35" t="str">
+        <x:v>Scope_Type</x:v>
+      </x:c>
+      <x:c r="B1" s="35" t="str">
+        <x:v>Scope_Value</x:v>
+      </x:c>
+      <x:c r="C1" s="35" t="str">
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="D1" s="35" t="str">
+        <x:v>Generation_Mode</x:v>
+      </x:c>
+      <x:c r="E1" s="35" t="str">
+        <x:v>Include_Raw</x:v>
+      </x:c>
+      <x:c r="F1" s="35" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A2" s="21" t="str">
+        <x:v>group</x:v>
+      </x:c>
+      <x:c r="B2" s="21" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="C2" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D2" s="21" t="str">
+        <x:v>all</x:v>
+      </x:c>
+      <x:c r="E2" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F2" s="21" t="str">
+        <x:v>Valueは原系列に加え、利用可能な差分・移動平均乖離をすべて使用</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="66" hidden="0" customHeight="1">
+      <x:c r="A3" s="21" t="str">
+        <x:v>group</x:v>
+      </x:c>
+      <x:c r="B3" s="21" t="str">
+        <x:v>Momentum</x:v>
+      </x:c>
+      <x:c r="C3" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D3" s="21" t="str">
+        <x:v>selected</x:v>
+      </x:c>
+      <x:c r="E3" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F3" s="21" t="str">
+        <x:v>MomentumはSelected=1の派生特徴量だけ使用</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A4" s="21" t="str">
+        <x:v>group</x:v>
+      </x:c>
+      <x:c r="B4" s="21" t="str">
+        <x:v>Quality</x:v>
+      </x:c>
+      <x:c r="C4" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D4" s="21" t="str">
+        <x:v>selected</x:v>
+      </x:c>
+      <x:c r="E4" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F4" s="21" t="str">
+        <x:v>派生特徴量は作成せず原系列のみ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A5" s="21" t="str">
+        <x:v>group</x:v>
+      </x:c>
+      <x:c r="B5" s="21" t="str">
+        <x:v>Growth</x:v>
+      </x:c>
+      <x:c r="C5" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D5" s="21" t="str">
+        <x:v>selected</x:v>
+      </x:c>
+      <x:c r="E5" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F5" s="21" t="str">
+        <x:v>派生特徴量は作成せず原系列のみ</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="4">
+    <x:dataValidation type="list" sqref="A2:A200">
+      <x:formula1>"group,factor"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="C2:C200">
+      <x:formula1>"0,1"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="D2:D200">
+      <x:formula1>"all,selected"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="E2:E200">
+      <x:formula1>"0,1"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="26" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="15" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="15" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="15" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="15" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="55" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="52.79999923706055" hidden="0" customHeight="1">
+      <x:c r="A1" s="35" t="str">
+        <x:v>Rule_ID</x:v>
+      </x:c>
+      <x:c r="B1" s="35" t="str">
+        <x:v>Scope_Type</x:v>
+      </x:c>
+      <x:c r="C1" s="35" t="str">
+        <x:v>Scope_Value</x:v>
+      </x:c>
+      <x:c r="D1" s="35" t="str">
+        <x:v>Feature_Type</x:v>
+      </x:c>
+      <x:c r="E1" s="35" t="str">
+        <x:v>Difference_Periods</x:v>
+      </x:c>
+      <x:c r="F1" s="35" t="str">
+        <x:v>Window_Periods</x:v>
+      </x:c>
+      <x:c r="G1" s="35" t="str">
+        <x:v>Min_Periods</x:v>
+      </x:c>
+      <x:c r="H1" s="35" t="str">
+        <x:v>Source_Lag_Periods</x:v>
+      </x:c>
+      <x:c r="I1" s="35" t="str">
+        <x:v>Exclude_Source_From_Baseline</x:v>
+      </x:c>
+      <x:c r="J1" s="35" t="str">
+        <x:v>Enabled</x:v>
+      </x:c>
+      <x:c r="K1" s="35" t="str">
+        <x:v>Selected</x:v>
+      </x:c>
+      <x:c r="L1" s="35" t="str">
+        <x:v>Direction_Mode</x:v>
+      </x:c>
+      <x:c r="M1" s="35" t="str">
+        <x:v>Custom_Direction</x:v>
+      </x:c>
+      <x:c r="N1" s="35" t="str">
+        <x:v>Description</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="132" hidden="0" customHeight="1">
+      <x:c r="A2" s="21" t="str">
+        <x:v>VAL_DIFF_1</x:v>
+      </x:c>
+      <x:c r="B2" s="21" t="str">
+        <x:v>group</x:v>
+      </x:c>
+      <x:c r="C2" s="21" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="D2" s="21" t="str">
+        <x:v>difference</x:v>
+      </x:c>
+      <x:c r="E2" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F2" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G2" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H2" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I2" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J2" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K2" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L2" s="21" t="str">
+        <x:v>inherit</x:v>
+      </x:c>
+      <x:c r="M2" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N2" s="21" t="str">
+        <x:v>スコア時点tにはx[t-1]-x[t-2]を格納。翌期リターンt+1まで最新情報から2時点離す。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="66" hidden="0" customHeight="1">
+      <x:c r="A3" s="21" t="str">
+        <x:v>VAL_MADEV_12</x:v>
+      </x:c>
+      <x:c r="B3" s="21" t="str">
+        <x:v>group</x:v>
+      </x:c>
+      <x:c r="C3" s="21" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="D3" s="21" t="str">
+        <x:v>rolling_mean_deviation</x:v>
+      </x:c>
+      <x:c r="E3" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F3" s="21" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G3" s="21" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H3" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I3" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J3" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K3" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L3" s="21" t="str">
+        <x:v>inherit</x:v>
+      </x:c>
+      <x:c r="M3" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N3" s="21" t="str">
+        <x:v>x[t-1]と、x[t-2]以前12期の移動平均との差。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A4" s="21" t="str">
+        <x:v>VAL_EXPDEV</x:v>
+      </x:c>
+      <x:c r="B4" s="21" t="str">
+        <x:v>group</x:v>
+      </x:c>
+      <x:c r="C4" s="21" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="D4" s="21" t="str">
+        <x:v>expanding_mean_deviation</x:v>
+      </x:c>
+      <x:c r="E4" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F4" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G4" s="21" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H4" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I4" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J4" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K4" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L4" s="21" t="str">
+        <x:v>inherit</x:v>
+      </x:c>
+      <x:c r="M4" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N4" s="21" t="str">
+        <x:v>x[t-1]と、x[t-2]以前の過去平均との差。Valueはall設定なので使用。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="79.19999694824219" hidden="0" customHeight="1">
+      <x:c r="A5" s="21" t="str">
+        <x:v>MOM_DIFF_1</x:v>
+      </x:c>
+      <x:c r="B5" s="21" t="str">
+        <x:v>group</x:v>
+      </x:c>
+      <x:c r="C5" s="21" t="str">
+        <x:v>Momentum</x:v>
+      </x:c>
+      <x:c r="D5" s="21" t="str">
+        <x:v>difference</x:v>
+      </x:c>
+      <x:c r="E5" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F5" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G5" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H5" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I5" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J5" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K5" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L5" s="21" t="str">
+        <x:v>inherit</x:v>
+      </x:c>
+      <x:c r="M5" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N5" s="21" t="str">
+        <x:v>Momentumの1期差分。selected設定のため使用。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A6" s="21" t="str">
+        <x:v>MOM_MADEV_6</x:v>
+      </x:c>
+      <x:c r="B6" s="21" t="str">
+        <x:v>group</x:v>
+      </x:c>
+      <x:c r="C6" s="21" t="str">
+        <x:v>Momentum</x:v>
+      </x:c>
+      <x:c r="D6" s="21" t="str">
+        <x:v>rolling_mean_deviation</x:v>
+      </x:c>
+      <x:c r="E6" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F6" s="21" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G6" s="21" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H6" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I6" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J6" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K6" s="21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L6" s="21" t="str">
+        <x:v>inherit</x:v>
+      </x:c>
+      <x:c r="M6" s="21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="N6" s="21" t="str">
+        <x:v>Momentumの6期移動平均乖離。selected=0のため現在は不使用。</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="7">
+    <x:dataValidation type="list" sqref="B2:B500">
+      <x:formula1>"group,factor"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="D2:D500">
+      <x:formula1>"difference,rolling_mean_deviation,rolling_mean_ratio,expanding_mean_deviation"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="I2:I500">
+      <x:formula1>"0,1"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="J2:J500">
+      <x:formula1>"0,1"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="K2:K500">
+      <x:formula1>"0,1"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="L2:L500">
+      <x:formula1>"inherit,reverse,custom"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="M2:M500">
+      <x:formula1>"-1,1"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>